--- a/Lab3/Lab3.xlsx
+++ b/Lab3/Lab3.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CFED475-0925-4130-AA1B-B88A3B825878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77EF7F7C-AF67-4241-B45F-7BD5A47FF304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EOW Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Comprehensive ECP BVA" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,21 +31,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="175">
   <si>
     <t>Test Case ID</t>
   </si>
   <si>
-    <t>Field Name</t>
+    <t>Test Scenario</t>
   </si>
   <si>
     <t>Precondition</t>
   </si>
   <si>
-    <t>Test Scenario</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
+    <t>Test Condition</t>
+  </si>
+  <si>
+    <t>Test Case Steps</t>
   </si>
   <si>
     <t>Test Data</t>
@@ -54,519 +54,508 @@
     <t>Expected Result</t>
   </si>
   <si>
+    <t>Actual Result Iteration 1</t>
+  </si>
+  <si>
+    <t>Status Iteration 1</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2</t>
+  </si>
+  <si>
+    <t>Status Iteration 2</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
     <t>TC001</t>
   </si>
   <si>
-    <t>Mobile Number</t>
-  </si>
-  <si>
-    <t>Login page open</t>
-  </si>
-  <si>
-    <t>Verify valid 10 digit mobile no</t>
-  </si>
-  <si>
-    <t>1. Open Browser
-2. Navigate to www.eow.com
-3. Click Login with Phone &amp; OTP
-4. Enter number
-5. Click Get OTP</t>
-  </si>
-  <si>
-    <t>Mobile: 9876543210</t>
-  </si>
-  <si>
-    <t>OTP should be sent</t>
+    <t>Person Age</t>
+  </si>
+  <si>
+    <t>Registration page available</t>
+  </si>
+  <si>
+    <t>Verify Person Age</t>
+  </si>
+  <si>
+    <t>Enter age and submit</t>
+  </si>
+  <si>
+    <t>Age:17</t>
+  </si>
+  <si>
+    <t>Invalid Age</t>
   </si>
   <si>
     <t>TC002</t>
   </si>
   <si>
-    <t>Verify 9 digit mobile no</t>
-  </si>
-  <si>
-    <t>Mobile: 987654321</t>
-  </si>
-  <si>
-    <t>show invalid mobile msg</t>
+    <t>Age:18</t>
+  </si>
+  <si>
+    <t>Proceed</t>
   </si>
   <si>
     <t>TC003</t>
   </si>
   <si>
-    <t>Verify 11 digit mobile no</t>
-  </si>
-  <si>
-    <t>Mobile: 98765432101</t>
-  </si>
-  <si>
-    <t>validation msg should come</t>
+    <t>Age:19</t>
   </si>
   <si>
     <t>TC004</t>
   </si>
   <si>
-    <t>Verify alphabets in mobile field</t>
-  </si>
-  <si>
-    <t>1. Open Browser
-2. Navigate to www.eow.com
-3. Click Login with Phone &amp; OTP
-4. Enter value
-5. Click Get OTP</t>
-  </si>
-  <si>
-    <t>Mobile: abcdefghij</t>
-  </si>
-  <si>
-    <t>should not accept</t>
+    <t>Age:50</t>
   </si>
   <si>
     <t>TC005</t>
   </si>
   <si>
-    <t>Verify blank mobile field</t>
-  </si>
-  <si>
-    <t>1. Open Browser
-2. Navigate to www.eow.com
-3. Click Login with Phone &amp; OTP
-5. Click Get OTP</t>
-  </si>
-  <si>
-    <t>Mobile: blank</t>
-  </si>
-  <si>
-    <t>required field msg</t>
+    <t>Age:98</t>
   </si>
   <si>
     <t>TC006</t>
   </si>
   <si>
-    <t>Get OTP Button</t>
-  </si>
-  <si>
-    <t>Verify Get OTP button</t>
-  </si>
-  <si>
-    <t>1. Open Browser
-2. Navigate to www.eow.com
-3. Click Login with Phone &amp; OTP
-4. Enter valid number
-5. Click Get OTP</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
-    <t>otp generated</t>
+    <t>Age:99</t>
   </si>
   <si>
     <t>TC007</t>
   </si>
   <si>
-    <t>OTP Field</t>
-  </si>
-  <si>
-    <t>OTP page displayed</t>
-  </si>
-  <si>
-    <t>Verify correct OTP</t>
-  </si>
-  <si>
-    <t>1. Enter OTP
-2. Click Confirm</t>
-  </si>
-  <si>
-    <t>OTP: valid</t>
-  </si>
-  <si>
-    <t>user logged in</t>
+    <t>Age:100</t>
   </si>
   <si>
     <t>TC008</t>
   </si>
   <si>
-    <t>Verify wrong OTP</t>
-  </si>
-  <si>
-    <t>OTP: 111111</t>
-  </si>
-  <si>
-    <t>wrong verification code</t>
+    <t>Age:0</t>
   </si>
   <si>
     <t>TC009</t>
   </si>
   <si>
-    <t>Verify blank OTP</t>
-  </si>
-  <si>
-    <t>1. Leave OTP blank
-2. Click Confirm</t>
-  </si>
-  <si>
-    <t>OTP: blank</t>
-  </si>
-  <si>
-    <t>enter otp msg</t>
+    <t>Age:-1</t>
   </si>
   <si>
     <t>TC010</t>
   </si>
   <si>
-    <t>Resend Code Link</t>
-  </si>
-  <si>
-    <t>Verify resend OTP</t>
-  </si>
-  <si>
-    <t>1. Wait 60 sec
-2. Click resend code</t>
-  </si>
-  <si>
-    <t>timeout reached</t>
-  </si>
-  <si>
-    <t>new otp should come</t>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Marks page available</t>
+  </si>
+  <si>
+    <t>Verify Exam Result</t>
+  </si>
+  <si>
+    <t>Enter marks and submit</t>
+  </si>
+  <si>
+    <t>Marks:-1</t>
+  </si>
+  <si>
+    <t>Invalid</t>
   </si>
   <si>
     <t>TC011</t>
   </si>
   <si>
-    <t>Cancel Button</t>
-  </si>
-  <si>
-    <t>Verify cancel button</t>
-  </si>
-  <si>
-    <t>1. Click Cancel</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>otp process cancelled</t>
+    <t>Marks:0</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
   <si>
     <t>TC012</t>
   </si>
   <si>
-    <t>Login with Phone &amp; OTP Button</t>
-  </si>
-  <si>
-    <t>Homepage open</t>
-  </si>
-  <si>
-    <t>Verify login popup opens</t>
-  </si>
-  <si>
-    <t>1. Click Login with Phone &amp; OTP</t>
-  </si>
-  <si>
-    <t>login screen displayed</t>
+    <t>Marks:59</t>
   </si>
   <si>
     <t>TC013</t>
   </si>
   <si>
-    <t>Submit a Free Ad</t>
-  </si>
-  <si>
-    <t>User logged in</t>
-  </si>
-  <si>
-    <t>Verify Submit a Free Ad button</t>
-  </si>
-  <si>
-    <t>1. Click Submit a Free Ad</t>
-  </si>
-  <si>
-    <t>ad form opens</t>
+    <t>Marks:60</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>TC014</t>
   </si>
   <si>
-    <t>Ad Title</t>
-  </si>
-  <si>
-    <t>Ad form open</t>
-  </si>
-  <si>
-    <t>Verify valid ad title</t>
-  </si>
-  <si>
-    <t>1. Enter title</t>
-  </si>
-  <si>
-    <t>Old iPhone 13</t>
-  </si>
-  <si>
-    <t>accepted</t>
+    <t>Marks:61</t>
   </si>
   <si>
     <t>TC015</t>
   </si>
   <si>
-    <t>Verify blank ad title</t>
-  </si>
-  <si>
-    <t>1. Leave title blank
-2. Submit</t>
-  </si>
-  <si>
-    <t>Blank</t>
-  </si>
-  <si>
-    <t>validation msg</t>
+    <t>Marks:80</t>
   </si>
   <si>
     <t>TC016</t>
   </si>
   <si>
-    <t>Price Field</t>
-  </si>
-  <si>
-    <t>Verify valid price</t>
-  </si>
-  <si>
-    <t>1. Enter price</t>
-  </si>
-  <si>
-    <t>5000</t>
+    <t>Marks:100</t>
   </si>
   <si>
     <t>TC017</t>
   </si>
   <si>
-    <t>Verify alphabet in price</t>
-  </si>
-  <si>
-    <t>five thousand</t>
-  </si>
-  <si>
-    <t>should show error</t>
+    <t>Marks:101</t>
   </si>
   <si>
     <t>TC018</t>
   </si>
   <si>
-    <t>Verify blank price</t>
-  </si>
-  <si>
-    <t>1. Leave blank</t>
-  </si>
-  <si>
-    <t>blank</t>
-  </si>
-  <si>
-    <t>required msg</t>
+    <t>Driver Age</t>
+  </si>
+  <si>
+    <t>Salary configured</t>
+  </si>
+  <si>
+    <t>Verify salary slab</t>
+  </si>
+  <si>
+    <t>Enter age</t>
+  </si>
+  <si>
+    <t>Age:24</t>
+  </si>
+  <si>
+    <t>15000</t>
   </si>
   <si>
     <t>TC019</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Verify description entry</t>
-  </si>
-  <si>
-    <t>1. Enter desc</t>
-  </si>
-  <si>
-    <t>Good condition</t>
+    <t>Age:25</t>
   </si>
   <si>
     <t>TC020</t>
   </si>
   <si>
-    <t>Submit Button</t>
-  </si>
-  <si>
-    <t>Ad form filled</t>
-  </si>
-  <si>
-    <t>Verify submit button</t>
-  </si>
-  <si>
-    <t>1. Fill fields
-2. Click Submit</t>
-  </si>
-  <si>
-    <t>valid ad details</t>
-  </si>
-  <si>
-    <t>otp screen displayed</t>
+    <t>Age:26</t>
   </si>
   <si>
     <t>TC021</t>
   </si>
   <si>
-    <t>Submit with mandatory field missing</t>
-  </si>
-  <si>
-    <t>1. Leave one mandatory field
-2. Submit</t>
-  </si>
-  <si>
-    <t>title blank</t>
-  </si>
-  <si>
-    <t>validation shown</t>
+    <t>Age:39</t>
   </si>
   <si>
     <t>TC022</t>
   </si>
   <si>
-    <t>Ad OTP</t>
-  </si>
-  <si>
-    <t>OTP screen displayed</t>
-  </si>
-  <si>
-    <t>Correct OTP after ad submit</t>
-  </si>
-  <si>
-    <t>1. Enter OTP
-2. Confirm</t>
-  </si>
-  <si>
-    <t>valid otp</t>
-  </si>
-  <si>
-    <t>Ad is successfully posted</t>
+    <t>Age:40</t>
+  </si>
+  <si>
+    <t>16500</t>
   </si>
   <si>
     <t>TC023</t>
   </si>
   <si>
-    <t>Incorrect OTP after ad submit</t>
-  </si>
-  <si>
-    <t>invalid otp</t>
-  </si>
-  <si>
-    <t>Ad not posted msg</t>
+    <t>Age:41</t>
   </si>
   <si>
     <t>TC024</t>
   </si>
   <si>
-    <t>Blank OTP during ad posting</t>
-  </si>
-  <si>
-    <t>1. Keep blank
-2. Confirm</t>
+    <t>Age:64</t>
   </si>
   <si>
     <t>TC025</t>
   </si>
   <si>
-    <t>Ad OTP screen</t>
-  </si>
-  <si>
-    <t>Verify resend code for ad otp</t>
-  </si>
-  <si>
-    <t>1. Wait timeout
-2. Click resend</t>
-  </si>
-  <si>
-    <t>timeout</t>
-  </si>
-  <si>
-    <t>new otp received</t>
+    <t>Age:65</t>
+  </si>
+  <si>
+    <t>15750</t>
   </si>
   <si>
     <t>TC026</t>
   </si>
   <si>
-    <t>Hyperlink URL</t>
-  </si>
-  <si>
-    <t>Browser open</t>
-  </si>
-  <si>
-    <t>Verify EOW url opens</t>
-  </si>
-  <si>
-    <t>1. Enter url</t>
-  </si>
-  <si>
-    <t>www.eow.com</t>
-  </si>
-  <si>
-    <t>homepage should open</t>
+    <t>Age:66</t>
   </si>
   <si>
     <t>TC027</t>
   </si>
   <si>
-    <t>Confirm Button</t>
-  </si>
-  <si>
-    <t>Verify confirm button is clickable</t>
-  </si>
-  <si>
-    <t>1. Enter OTP
-2. Click confirm</t>
-  </si>
-  <si>
-    <t>next page displayed</t>
+    <t>Customer Age</t>
+  </si>
+  <si>
+    <t>Sale active</t>
+  </si>
+  <si>
+    <t>Verify winter sale eligibility</t>
+  </si>
+  <si>
+    <t>Age:7</t>
+  </si>
+  <si>
+    <t>Discount</t>
   </si>
   <si>
     <t>TC028</t>
   </si>
   <si>
-    <t>Verify special chars in mobile no</t>
-  </si>
-  <si>
-    <t>Enter @#$%^</t>
-  </si>
-  <si>
-    <t>@#$%^</t>
+    <t>Age:8</t>
+  </si>
+  <si>
+    <t>No Discount</t>
   </si>
   <si>
     <t>TC029</t>
   </si>
   <si>
-    <t>Session Timeout</t>
-  </si>
-  <si>
-    <t>Verify OTP expiry after 60 sec</t>
-  </si>
-  <si>
-    <t>1. Wait &gt;60 sec
-2. Enter old otp</t>
-  </si>
-  <si>
-    <t>expired otp</t>
-  </si>
-  <si>
-    <t>otp expired msg</t>
+    <t>Age:34</t>
   </si>
   <si>
     <t>TC030</t>
   </si>
   <si>
-    <t>End to End</t>
-  </si>
-  <si>
-    <t>Application available</t>
-  </si>
-  <si>
-    <t>Verify complete ad posting flow</t>
-  </si>
-  <si>
-    <t>Login -&gt; Submit Ad -&gt; Verify OTP</t>
-  </si>
-  <si>
-    <t>all valid data</t>
-  </si>
-  <si>
-    <t>ad posted successfully</t>
+    <t>Age:35</t>
+  </si>
+  <si>
+    <t>TC031</t>
+  </si>
+  <si>
+    <t>Age:36</t>
+  </si>
+  <si>
+    <t>TC032</t>
+  </si>
+  <si>
+    <t>Age:44</t>
+  </si>
+  <si>
+    <t>TC033</t>
+  </si>
+  <si>
+    <t>Age:45</t>
+  </si>
+  <si>
+    <t>TC034</t>
+  </si>
+  <si>
+    <t>Age:60</t>
+  </si>
+  <si>
+    <t>TC035</t>
+  </si>
+  <si>
+    <t>Age:61</t>
+  </si>
+  <si>
+    <t>TC036</t>
+  </si>
+  <si>
+    <t>Order Quantity</t>
+  </si>
+  <si>
+    <t>Ordering available</t>
+  </si>
+  <si>
+    <t>Verify cartridge order</t>
+  </si>
+  <si>
+    <t>Enter quantity</t>
+  </si>
+  <si>
+    <t>Qty:0</t>
+  </si>
+  <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>TC037</t>
+  </si>
+  <si>
+    <t>Qty:4</t>
+  </si>
+  <si>
+    <t>TC038</t>
+  </si>
+  <si>
+    <t>Qty:5</t>
+  </si>
+  <si>
+    <t>Accept</t>
+  </si>
+  <si>
+    <t>TC039</t>
+  </si>
+  <si>
+    <t>Qty:6</t>
+  </si>
+  <si>
+    <t>TC040</t>
+  </si>
+  <si>
+    <t>Qty:99</t>
+  </si>
+  <si>
+    <t>Accept No Discount</t>
+  </si>
+  <si>
+    <t>TC041</t>
+  </si>
+  <si>
+    <t>Qty:100</t>
+  </si>
+  <si>
+    <t>20% Discount</t>
+  </si>
+  <si>
+    <t>TC042</t>
+  </si>
+  <si>
+    <t>Qty:101</t>
+  </si>
+  <si>
+    <t>TC043</t>
+  </si>
+  <si>
+    <t>Qty:150</t>
+  </si>
+  <si>
+    <t>TC044</t>
+  </si>
+  <si>
+    <t>Years of Service</t>
+  </si>
+  <si>
+    <t>Bonus module available</t>
+  </si>
+  <si>
+    <t>Verify bonus calculation</t>
+  </si>
+  <si>
+    <t>Enter service years</t>
+  </si>
+  <si>
+    <t>Years:0</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>TC045</t>
+  </si>
+  <si>
+    <t>Years:1.9</t>
+  </si>
+  <si>
+    <t>TC046</t>
+  </si>
+  <si>
+    <t>Years:2</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t>TC047</t>
+  </si>
+  <si>
+    <t>Years:2.1</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>TC048</t>
+  </si>
+  <si>
+    <t>Years:4.9</t>
+  </si>
+  <si>
+    <t>TC049</t>
+  </si>
+  <si>
+    <t>Years:5</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>TC050</t>
+  </si>
+  <si>
+    <t>Years:9.9</t>
+  </si>
+  <si>
+    <t>TC051</t>
+  </si>
+  <si>
+    <t>Years:10</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>TC052</t>
+  </si>
+  <si>
+    <t>Years:15</t>
+  </si>
+  <si>
+    <t>TC053</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Module available</t>
+  </si>
+  <si>
+    <t>Additional ECP validation</t>
+  </si>
+  <si>
+    <t>Enter value</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>TC054</t>
+  </si>
+  <si>
+    <t>Invalid Marks</t>
+  </si>
+  <si>
+    <t>TC055</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>-5</t>
+  </si>
+  <si>
+    <t>TC056</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>TC057</t>
+  </si>
+  <si>
+    <t>-1</t>
   </si>
 </sst>
 </file>
@@ -596,7 +585,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -612,10 +601,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -920,725 +908,1375 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="100.85546875" customWidth="1"/>
-    <col min="6" max="7" width="35" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="76.5">
-      <c r="A2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="76.5">
-      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
       <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="76.5">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
       <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="76.5">
-      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="60.75">
-      <c r="A6" t="s">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="F6" t="s">
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
         <v>30</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="76.5">
-      <c r="A7" t="s">
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="30.75">
-      <c r="A8" t="s">
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D11" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E11" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F11" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G11" t="s">
         <v>42</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H11" t="s">
         <v>43</v>
       </c>
-      <c r="G8" t="s">
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="30.75">
-      <c r="A9" t="s">
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
         <v>45</v>
       </c>
-      <c r="B9" t="s">
+      <c r="H12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E13" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30.75">
-      <c r="A10" t="s">
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" t="s">
         <v>49</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E14" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="H14" t="s">
         <v>51</v>
       </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" t="s">
         <v>52</v>
       </c>
-      <c r="G10" t="s">
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="30.75">
-      <c r="A11" t="s">
+      <c r="H15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
         <v>55</v>
       </c>
-      <c r="C11" t="s">
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
         <v>57</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" t="s">
         <v>58</v>
       </c>
-      <c r="G11" t="s">
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" t="s">
         <v>60</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C19" t="s">
         <v>61</v>
       </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="D19" t="s">
         <v>62</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E19" t="s">
         <v>63</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F19" t="s">
         <v>64</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G19" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="H19" t="s">
         <v>66</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" t="s">
         <v>67</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" t="s">
         <v>68</v>
       </c>
-      <c r="D13" t="s">
+      <c r="H20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" t="s">
         <v>69</v>
       </c>
-      <c r="E13" t="s">
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" t="s">
         <v>70</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s">
         <v>64</v>
       </c>
-      <c r="G13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="G22" t="s">
         <v>72</v>
       </c>
-      <c r="B14" t="s">
+      <c r="H22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" t="s">
         <v>73</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" t="s">
         <v>74</v>
       </c>
-      <c r="D14" t="s">
+      <c r="H23" t="s">
         <v>75</v>
       </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" t="s">
         <v>76</v>
       </c>
-      <c r="F14" t="s">
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" t="s">
         <v>64</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="H24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
         <v>79</v>
       </c>
-      <c r="C15" t="s">
+      <c r="H25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" t="s">
         <v>80</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" t="s">
         <v>81</v>
       </c>
-      <c r="E15" t="s">
+      <c r="H26" t="s">
         <v>82</v>
       </c>
-      <c r="F15" t="s">
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" t="s">
         <v>83</v>
       </c>
-      <c r="G15" t="s">
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="30.75">
-      <c r="A16" t="s">
+      <c r="H27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" t="s">
         <v>85</v>
       </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C28" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D28" t="s">
         <v>87</v>
       </c>
-      <c r="F16" t="s">
+      <c r="E28" t="s">
         <v>88</v>
       </c>
-      <c r="G16" t="s">
+      <c r="F28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="H28" t="s">
         <v>90</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" t="s">
         <v>91</v>
       </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" t="s">
         <v>92</v>
       </c>
-      <c r="E17" t="s">
+      <c r="H29" t="s">
         <v>93</v>
       </c>
-      <c r="F17" t="s">
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" t="s">
         <v>94</v>
       </c>
-      <c r="G17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" t="s">
         <v>95</v>
       </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="H30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" t="s">
         <v>96</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" t="s">
         <v>93</v>
       </c>
-      <c r="F18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" t="s">
         <v>99</v>
       </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="H32" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" t="s">
         <v>100</v>
       </c>
-      <c r="E19" t="s">
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" t="s">
         <v>101</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" t="s">
         <v>102</v>
       </c>
-      <c r="G19" t="s">
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
+      <c r="H34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" t="s">
         <v>104</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" t="s">
         <v>105</v>
       </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="H35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" t="s">
         <v>106</v>
       </c>
-      <c r="E20" t="s">
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" t="s">
+        <v>88</v>
+      </c>
+      <c r="F36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36" t="s">
         <v>107</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" t="s">
         <v>108</v>
       </c>
-      <c r="G20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30.75">
-      <c r="A21" t="s">
+      <c r="C37" t="s">
         <v>109</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D37" t="s">
         <v>110</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E37" t="s">
         <v>111</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F37" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="G37" t="s">
         <v>113</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H37" t="s">
         <v>114</v>
       </c>
-      <c r="G21" t="s">
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="30.75">
-      <c r="A22" t="s">
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
         <v>116</v>
       </c>
-      <c r="B22" t="s">
+      <c r="H38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" t="s">
         <v>110</v>
       </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" t="s">
         <v>118</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H39" t="s">
         <v>119</v>
       </c>
-      <c r="G22" t="s">
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="30.75">
-      <c r="A23" t="s">
+      <c r="C40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" t="s">
+        <v>112</v>
+      </c>
+      <c r="G40" t="s">
         <v>121</v>
       </c>
-      <c r="B23" t="s">
+      <c r="H40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" t="s">
         <v>122</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41" t="s">
         <v>123</v>
       </c>
-      <c r="D23" t="s">
+      <c r="H41" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="2" t="s">
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" t="s">
         <v>125</v>
       </c>
-      <c r="F23" t="s">
+      <c r="C42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" t="s">
         <v>126</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H42" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30.75">
-      <c r="A24" t="s">
+    <row r="43" spans="2:8">
+      <c r="B43" t="s">
         <v>128</v>
       </c>
-      <c r="B24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" t="s">
+        <v>112</v>
+      </c>
+      <c r="G43" t="s">
         <v>129</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="H43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" t="s">
         <v>130</v>
       </c>
-      <c r="G24" t="s">
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G44" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="30.75">
-      <c r="A25" t="s">
+      <c r="H44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" t="s">
         <v>132</v>
       </c>
-      <c r="B25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C45" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="D45" t="s">
         <v>134</v>
       </c>
-      <c r="F25" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30.75">
-      <c r="A26" t="s">
+      <c r="E45" t="s">
         <v>135</v>
       </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="F45" t="s">
         <v>136</v>
       </c>
-      <c r="D26" t="s">
+      <c r="G45" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="H45" t="s">
         <v>138</v>
       </c>
-      <c r="F26" t="s">
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" t="s">
         <v>139</v>
       </c>
-      <c r="G26" t="s">
+      <c r="C46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" t="s">
+        <v>135</v>
+      </c>
+      <c r="F46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
+      <c r="H46" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" t="s">
         <v>141</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" t="s">
         <v>142</v>
       </c>
-      <c r="C27" t="s">
+      <c r="H47" t="s">
         <v>143</v>
       </c>
-      <c r="D27" t="s">
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" t="s">
         <v>144</v>
       </c>
-      <c r="E27" t="s">
+      <c r="C48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>134</v>
+      </c>
+      <c r="E48" t="s">
+        <v>135</v>
+      </c>
+      <c r="F48" t="s">
+        <v>136</v>
+      </c>
+      <c r="G48" t="s">
         <v>145</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H48" t="s">
         <v>146</v>
       </c>
-      <c r="G27" t="s">
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="30.75">
-      <c r="A28" t="s">
+      <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" t="s">
+        <v>135</v>
+      </c>
+      <c r="F49" t="s">
+        <v>136</v>
+      </c>
+      <c r="G49" t="s">
         <v>148</v>
       </c>
-      <c r="B28" t="s">
+      <c r="H49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" t="s">
         <v>149</v>
       </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C50" t="s">
+        <v>133</v>
+      </c>
+      <c r="D50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F50" t="s">
+        <v>136</v>
+      </c>
+      <c r="G50" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="H50" t="s">
         <v>151</v>
       </c>
-      <c r="F28" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" t="s">
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
+      <c r="C51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" t="s">
+        <v>134</v>
+      </c>
+      <c r="E51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" t="s">
+        <v>136</v>
+      </c>
+      <c r="G51" t="s">
         <v>153</v>
       </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="H51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" t="s">
         <v>154</v>
       </c>
-      <c r="E29" t="s">
+      <c r="C52" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" t="s">
+        <v>134</v>
+      </c>
+      <c r="E52" t="s">
+        <v>135</v>
+      </c>
+      <c r="F52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G52" t="s">
         <v>155</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H52" t="s">
         <v>156</v>
       </c>
-      <c r="G29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30.75">
-      <c r="A30" t="s">
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" t="s">
         <v>157</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C53" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" t="s">
+        <v>135</v>
+      </c>
+      <c r="F53" t="s">
+        <v>136</v>
+      </c>
+      <c r="G53" t="s">
         <v>158</v>
       </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="H53" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="C54" t="s">
         <v>160</v>
       </c>
-      <c r="F30" t="s">
+      <c r="D54" t="s">
         <v>161</v>
       </c>
-      <c r="G30" t="s">
+      <c r="E54" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
+      <c r="F54" t="s">
         <v>163</v>
       </c>
-      <c r="B31" t="s">
+      <c r="G54" t="s">
         <v>164</v>
       </c>
-      <c r="C31" t="s">
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="B55" t="s">
         <v>165</v>
       </c>
-      <c r="D31" t="s">
+      <c r="C55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" t="s">
+        <v>162</v>
+      </c>
+      <c r="F55" t="s">
+        <v>163</v>
+      </c>
+      <c r="G55" t="s">
+        <v>164</v>
+      </c>
+      <c r="H55" t="s">
         <v>166</v>
       </c>
-      <c r="E31" t="s">
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" t="s">
         <v>167</v>
       </c>
-      <c r="F31" t="s">
+      <c r="C56" t="s">
         <v>168</v>
       </c>
-      <c r="G31" t="s">
+      <c r="D56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" t="s">
+        <v>162</v>
+      </c>
+      <c r="F56" t="s">
+        <v>163</v>
+      </c>
+      <c r="G56" t="s">
         <v>169</v>
+      </c>
+      <c r="H56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" t="s">
+        <v>162</v>
+      </c>
+      <c r="F57" t="s">
+        <v>163</v>
+      </c>
+      <c r="G57" t="s">
+        <v>172</v>
+      </c>
+      <c r="H57" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" t="s">
+        <v>162</v>
+      </c>
+      <c r="F58" t="s">
+        <v>163</v>
+      </c>
+      <c r="G58" t="s">
+        <v>174</v>
+      </c>
+      <c r="H58" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
